--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -613,28 +613,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 강사 공지사항</t>
+          <t>평생교육원 신규 강좌 개설 제안서 안내</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>부산대학교 미래시민교육원</t>
+          <t>울산대학교 평생교육원 공지사항</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>부산, 경남, 밀양, 양산</t>
+          <t>울산, 경남</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>미래시민교육원 2026학년도 2학기 공지사항을 반드시 확인하시어 기간내 처리하여 주시기 바랍니다. 1. 2026학년도 2학기 강사 공지사항 [붙임 1] 자료를 확인하시고 수업 운영에 만전을 기하여 주시기 바랍니다. 2. 아동학대 및 긴급복지지원 신고의무자 교육 안내 [붙임 1] 자료를 확인하시고 2026. 9. 30.(수) 까지 수료증을 제출하여 주시기 바랍니다. º 이수대상: 부산대학교 미래시민교육원 개설강좌 강사 전원 º 이수과목: 아동학대 신고의무자 및 공공부문 종사자 아동학대 예방교육 (1시간)(2026년) 긴급복지지원 신고의무자 교육 (1시간)(2026년) ※ 위 2개 교육과정 필수 이수 하셔야 합니다. º 제출처: zoomboy@pusan.ac.kr ※ 매년 이수해야하는 법정의무교육입니다.(1년에 1회 제출) 3. 프리랜서(강사) 근로 계약 체결 º 대상: 부산대학교 미래시민교육원 개설강좌 강사 º 계약 체결 기한: 2026년 2학기 본인 강의 첫 수업 전까지 제출 º 계약 방법: 서면 계약 ※ 기간내 스캔 파일 메일로 제출 요망(제출처: zoomboy@pusan.ac.kr)</t>
+          <t>울산대학교 평생교육원에서는 참신한 신규 강좌를 모집하오니 관심 있는 강사님들의 많은 신청 바랍니다. 1. 지원 분야 - 평생 교육 관련 전 분야 2. 제출 방법 - 울산대학교 평생교육원 홈페이지 강좌개설제안서 클릭 - 서류 제출 후 전화 확인 - 접수된 개별 신청서는 평생교육원 운영위원회 심의를 통해 최종 개설 확정 후 개별 연락 드립니다. 3. 제출 기한 -2027년 1학기 : 2026.10.01 09:00 ~ 2026.11.20 17:00 -2027년 2학기 : 2027.04.01 09:00 ~ 2027.05.21 17:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -643,50 +643,11 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://sce.pusan.ac.kr/page?menuCD=000000000000561&amp;mode=DETAIL&amp;seq=2594&amp;mainbbsTabIndex=&amp;typeSeqNo=1</t>
+          <t>https://cec.ulsan.ac.kr/cec/3978?action=view&amp;no=270342</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>평생교육원 신규 강좌 개설 제안서 안내</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>울산대학교 평생교육원 공지사항</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>울산, 경남</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>울산대학교 평생교육원에서는 참신한 신규 강좌를 모집하오니 관심 있는 강사님들의 많은 신청 바랍니다. 1. 지원 분야 - 평생 교육 관련 전 분야 2. 제출 방법 - 울산대학교 평생교육원 홈페이지 강좌개설제안서 클릭 - 서류 제출 후 전화 확인 - 접수된 개별 신청서는 평생교육원 운영위원회 심의를 통해 최종 개설 확정 후 개별 연락 드립니다. 3. 제출 기한 -2027년 1학기 : 2026.10.01 09:00 ~ 2026.11.20 17:00 -2027년 2학기 : 2027.04.01 09:00 ~ 2027.05.21 17:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://cec.ulsan.ac.kr/cec/3978?action=view&amp;no=270342</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -613,28 +613,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>평생교육원 신규 강좌 개설 제안서 안내</t>
+          <t>[김해대학교] 국제교류원 한국어강사 신규 채용 공고</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>울산대학교 평생교육원 공지사항</t>
+          <t>김해대학교 평생직업교육원</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>울산, 경남</t>
+          <t>경남, 김해</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>울산대학교 평생교육원에서는 참신한 신규 강좌를 모집하오니 관심 있는 강사님들의 많은 신청 바랍니다. 1. 지원 분야 - 평생 교육 관련 전 분야 2. 제출 방법 - 울산대학교 평생교육원 홈페이지 강좌개설제안서 클릭 - 서류 제출 후 전화 확인 - 접수된 개별 신청서는 평생교육원 운영위원회 심의를 통해 최종 개설 확정 후 개별 연락 드립니다. 3. 제출 기한 -2027년 1학기 : 2026.10.01 09:00 ~ 2026.11.20 17:00 -2027년 2학기 : 2027.04.01 09:00 ~ 2027.05.21 17:00</t>
+          <t>[김해대학교] 국제교류원 한국어강사 신규 채용 공고 작성자 기획처 등록일 2026-09-07 20:32:05 조회수 145 분류 채용 게시글의 공지시작일, 공지마감일에 대한 안내입니다. 공지시작일 2026-09-07 공지마감일 2026-09-14 [김해대학교] 국제교류원 한국어강사 신규 채용 공고 국제교류원 한국어강사 신규 채용 공고 (0명) 📋 주요업무 • 외국인 유학생(어학연수생) 대상 한국어 교육 및 강의 • 외국인 유학생(어학연수생) 대상 상담 및 관리 등 업무 전반 • 국제교류원(한국어학당) 부서 소속 📋 자격요건 • 경력 무관 (신입 지원 가능) • 대학교졸업(4년)이상 • 한국어교원자격증 2급(필수) • 한국어교원자격증 3급(필수) 📋 우대사항 • 타 대학에서 한국어교육 및 강의 경험이 있으신 분 🏠 근무조건 • 고용형태 : 계약직 (기간제) • 급여 : 시급 31,500원 • 근무지 : 경남 김해시 삼안로112번길 198 김해대학교 • 근무시간 : 09:00~13:00 주 5일(월~금) (근무요일은 채용 확정 후 결정) 🚀 채용절차 접수기간 : 2026-09-07(월) 20시 ~ 2026-09-14(월) 15시 제출서류 : 자사양식 이력서 접수방법 : 홈페이지 지원 [ https://apply.gimhae.ac.kr/ ]로 접속해서 지원 (1)지원하고자 하는 응시분야는 [ 한국어학당 ]를 선택해서 지원하기를 클릭하신후 내용 입력하시고 "최종제출" 하시면 됩니다. (2)공고기간 중이라도 적격자가 있으면 면접을 진행할 수 있으며, 채용이 확정되면 조기 마감될 수 있습니다. (3)면접 대상자는 "접수 마감 후 5일이내" 서류전형 합격자에 한하여 문자로 개별 통보 를 해드립니다. 전형절차 : [1]서류전형 → [2]1차면접 (서류 합격자에 한해 개별 통보) → [3]최종합격 (합격자에게 개별 통보 예정) 🛎️ 유의사항 • 입사지원 서류에 허위사실이 발견될 경우, 채용확정 이후라도 채용이 취소될 수 있습니다. • 사립학교 직원 임용에 결격 사유가 없는 사람(남자의 경우 병역을 필하였거나 면제인 사람) • 위 일정은 학교의 사정에 따라 변경 될 수 있으며, 적격자가 없을 경우 채용하지 않을 수 있습니다. • 기타 문의 사항은 국제교류원 사무실 (055-320-1636) 로 문의 하여 주시기 바랍니다.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -643,11 +643,50 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://cec.ulsan.ac.kr/cec/3978?action=view&amp;no=270342</t>
+          <t>https://www.gimhae.ac.kr/www/board/postview/47/17598?page=1&amp;currentPage=1&amp;SchColumn=SC3&amp;SchValue=&amp;CategorySeq=&amp;RecordCount=10</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>평생교육원 신규 강좌 개설 제안서 안내</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>울산대학교 평생교육원 공지사항</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>울산, 경남</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>울산대학교 평생교육원에서는 참신한 신규 강좌를 모집하오니 관심 있는 강사님들의 많은 신청 바랍니다. 1. 지원 분야 - 평생 교육 관련 전 분야 2. 제출 방법 - 울산대학교 평생교육원 홈페이지 강좌개설제안서 클릭 - 서류 제출 후 전화 확인 - 접수된 개별 신청서는 평생교육원 운영위원회 심의를 통해 최종 개설 확정 후 개별 연락 드립니다. 3. 제출 기한 -2027년 1학기 : 2026.10.01 09:00 ~ 2026.11.20 17:00 -2027년 2학기 : 2027.04.01 09:00 ~ 2027.05.21 17:00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://cec.ulsan.ac.kr/cec/3978?action=view&amp;no=270342</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -613,28 +613,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[김해대학교] 국제교류원 한국어강사 신규 채용 공고</t>
+          <t>평생교육원 신규 강좌 개설 제안서 안내</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>김해대학교 평생직업교육원</t>
+          <t>울산대학교 평생교육원 공지사항</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>경남, 김해</t>
+          <t>울산, 경남</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[김해대학교] 국제교류원 한국어강사 신규 채용 공고 작성자 기획처 등록일 2026-09-07 20:32:05 조회수 145 분류 채용 게시글의 공지시작일, 공지마감일에 대한 안내입니다. 공지시작일 2026-09-07 공지마감일 2026-09-14 [김해대학교] 국제교류원 한국어강사 신규 채용 공고 국제교류원 한국어강사 신규 채용 공고 (0명) 📋 주요업무 • 외국인 유학생(어학연수생) 대상 한국어 교육 및 강의 • 외국인 유학생(어학연수생) 대상 상담 및 관리 등 업무 전반 • 국제교류원(한국어학당) 부서 소속 📋 자격요건 • 경력 무관 (신입 지원 가능) • 대학교졸업(4년)이상 • 한국어교원자격증 2급(필수) • 한국어교원자격증 3급(필수) 📋 우대사항 • 타 대학에서 한국어교육 및 강의 경험이 있으신 분 🏠 근무조건 • 고용형태 : 계약직 (기간제) • 급여 : 시급 31,500원 • 근무지 : 경남 김해시 삼안로112번길 198 김해대학교 • 근무시간 : 09:00~13:00 주 5일(월~금) (근무요일은 채용 확정 후 결정) 🚀 채용절차 접수기간 : 2026-09-07(월) 20시 ~ 2026-09-14(월) 15시 제출서류 : 자사양식 이력서 접수방법 : 홈페이지 지원 [ https://apply.gimhae.ac.kr/ ]로 접속해서 지원 (1)지원하고자 하는 응시분야는 [ 한국어학당 ]를 선택해서 지원하기를 클릭하신후 내용 입력하시고 "최종제출" 하시면 됩니다. (2)공고기간 중이라도 적격자가 있으면 면접을 진행할 수 있으며, 채용이 확정되면 조기 마감될 수 있습니다. (3)면접 대상자는 "접수 마감 후 5일이내" 서류전형 합격자에 한하여 문자로 개별 통보 를 해드립니다. 전형절차 : [1]서류전형 → [2]1차면접 (서류 합격자에 한해 개별 통보) → [3]최종합격 (합격자에게 개별 통보 예정) 🛎️ 유의사항 • 입사지원 서류에 허위사실이 발견될 경우, 채용확정 이후라도 채용이 취소될 수 있습니다. • 사립학교 직원 임용에 결격 사유가 없는 사람(남자의 경우 병역을 필하였거나 면제인 사람) • 위 일정은 학교의 사정에 따라 변경 될 수 있으며, 적격자가 없을 경우 채용하지 않을 수 있습니다. • 기타 문의 사항은 국제교류원 사무실 (055-320-1636) 로 문의 하여 주시기 바랍니다.</t>
+          <t>울산대학교 평생교육원에서는 참신한 신규 강좌를 모집하오니 관심 있는 강사님들의 많은 신청 바랍니다. 1. 지원 분야 - 평생 교육 관련 전 분야 2. 제출 방법 - 울산대학교 평생교육원 홈페이지 강좌개설제안서 클릭 - 서류 제출 후 전화 확인 - 접수된 개별 신청서는 평생교육원 운영위원회 심의를 통해 최종 개설 확정 후 개별 연락 드립니다. 3. 제출 기한 -2027년 1학기 : 2026.10.01 09:00 ~ 2026.11.20 17:00 -2027년 2학기 : 2027.04.01 09:00 ~ 2027.05.21 17:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -643,50 +643,11 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.gimhae.ac.kr/www/board/postview/47/17598?page=1&amp;currentPage=1&amp;SchColumn=SC3&amp;SchValue=&amp;CategorySeq=&amp;RecordCount=10</t>
+          <t>https://cec.ulsan.ac.kr/cec/3978?action=view&amp;no=270342</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>평생교육원 신규 강좌 개설 제안서 안내</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>울산대학교 평생교육원 공지사항</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>울산, 경남</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2027-05-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>울산대학교 평생교육원에서는 참신한 신규 강좌를 모집하오니 관심 있는 강사님들의 많은 신청 바랍니다. 1. 지원 분야 - 평생 교육 관련 전 분야 2. 제출 방법 - 울산대학교 평생교육원 홈페이지 강좌개설제안서 클릭 - 서류 제출 후 전화 확인 - 접수된 개별 신청서는 평생교육원 운영위원회 심의를 통해 최종 개설 확정 후 개별 연락 드립니다. 3. 제출 기한 -2027년 1학기 : 2026.10.01 09:00 ~ 2026.11.20 17:00 -2027년 2학기 : 2027.04.01 09:00 ~ 2027.05.21 17:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://cec.ulsan.ac.kr/cec/3978?action=view&amp;no=270342</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -613,28 +613,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>평생교육원 신규 강좌 개설 제안서 안내</t>
+          <t>2026년 학점은행제 교강사 법정의무교육 실시 안내</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>울산대학교 평생교육원 공지사항</t>
+          <t>동의대학교 미래교육원</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>울산, 경남</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>울산대학교 평생교육원에서는 참신한 신규 강좌를 모집하오니 관심 있는 강사님들의 많은 신청 바랍니다. 1. 지원 분야 - 평생 교육 관련 전 분야 2. 제출 방법 - 울산대학교 평생교육원 홈페이지 강좌개설제안서 클릭 - 서류 제출 후 전화 확인 - 접수된 개별 신청서는 평생교육원 운영위원회 심의를 통해 최종 개설 확정 후 개별 연락 드립니다. 3. 제출 기한 -2027년 1학기 : 2026.10.01 09:00 ~ 2026.11.20 17:00 -2027년 2학기 : 2027.04.01 09:00 ~ 2027.05.21 17:00</t>
+          <t>2026년 학점은행제 교강사 법정의무교육 실시 안내 「아동복지법」제26조 제3항 및 「긴급복지지원법」제7조 제5항,「장애인복지법」제59조의 4 제6항 및 7항에 따라 아동학대 신고의무자 교육, 예방교육 및 긴급복지 신고의무자 교육, 장애인학대 신고의무자 교육을 다음과 같이 실시하고자 합니다. 반드시 기한내에 이수하시고 수료증(이수증)을 제출하여 주시기 바랍니다.(교육방법 및 수료증 출력 방법: 첨부파일 참조) [주의사항] 의무교육을 이수하지 않으신 분들은 다음학기부터 강의가 불가하니 반드시 기간내 제출하시기 바랍니다. 교육에 따라 수료증 출력은 과정 이수 후 1~2일 이후 가능할 수 있으므로 이점 참고하여 이수하시기 바랍니다. 2025년 의무교육 이수자도 2026년 의무교육을 반드시 이수하여야 합니다. (2026년도에 이수한 의무교육만 인정) 1. 교육명 가. 아동학대 신고의무자 교육 및 공공부문 아동학대 예방교육(1시간) 나. 긴급복지지원 신고의무자 교육(1시간) 다. 장애인학대 및 장애인 대상 성범죄 신고의무자 교육(1시간) 2. 수료증(이수증): 총 3개(아동학대 1개, 긴급지원(복지) 1개, 장애인학대 1개) 가. 제출 기한: 2026. 11. 6.(금)까지 나. 제출 방법: PDF 파일 이메일 제출(dione017@deu.ac.kr) 다. 파일 제출이 불가능하신 분들은 인쇄하여 행정지원실(지천관 207호) 직접 제출 3. 대상자: 학점은행제 교강사 전체 4. 교육방법: 세부내용 첨부파일 참조 - 아동학대 / 장애인학대: https://sll.seoul.go.kr - 긴급복지지원: https://edu.kohi.or.kr/in 5. 비고 가. 반드시 회원가입/로그인 후 수강하셔야 수료증(이수증) 발급이 가능합니다. 나. 타기관에서 2026년 의무교육을 이수하신 분들은 해당 수료증을 제출하시면 됩니다.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -643,11 +643,50 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://cec.ulsan.ac.kr/cec/3978?action=view&amp;no=270342</t>
+          <t>https://lifelong.deu.ac.kr/fro-end/dep-05/5100/view/657</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>평생교육원 신규 강좌 개설 제안서 안내</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>울산대학교 평생교육원 공지사항</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>울산, 경남</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>울산대학교 평생교육원에서는 참신한 신규 강좌를 모집하오니 관심 있는 강사님들의 많은 신청 바랍니다. 1. 지원 분야 - 평생 교육 관련 전 분야 2. 제출 방법 - 울산대학교 평생교육원 홈페이지 강좌개설제안서 클릭 - 서류 제출 후 전화 확인 - 접수된 개별 신청서는 평생교육원 운영위원회 심의를 통해 최종 개설 확정 후 개별 연락 드립니다. 3. 제출 기한 -2027년 1학기 : 2026.10.01 09:00 ~ 2026.11.20 17:00 -2027년 2학기 : 2027.04.01 09:00 ~ 2027.05.21 17:00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://cec.ulsan.ac.kr/cec/3978?action=view&amp;no=270342</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -652,28 +652,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>평생교육원 신규 강좌 개설 제안서 안내</t>
+          <t>2026학년도 2학기 평생교육과정 동계방학특강 개설 제안 공모 안내</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>울산대학교 평생교육원 공지사항</t>
+          <t>마산대학교 평생교육원 공지사항</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>울산, 경남</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>울산대학교 평생교육원에서는 참신한 신규 강좌를 모집하오니 관심 있는 강사님들의 많은 신청 바랍니다. 1. 지원 분야 - 평생 교육 관련 전 분야 2. 제출 방법 - 울산대학교 평생교육원 홈페이지 강좌개설제안서 클릭 - 서류 제출 후 전화 확인 - 접수된 개별 신청서는 평생교육원 운영위원회 심의를 통해 최종 개설 확정 후 개별 연락 드립니다. 3. 제출 기한 -2027년 1학기 : 2026.10.01 09:00 ~ 2026.11.20 17:00 -2027년 2학기 : 2027.04.01 09:00 ~ 2027.05.21 17:00</t>
+          <t>2026학년도 2학기 평생교육과정 동계방학특강 개설 제안 공모 안내 작성자 create 조혜인 작성일 access_time 2026.10.26 15:16 조회수 visibility 11 첨부파일 2026학년도 2학기 동계방학특강 강의계획서 및 강사추천서.hwp [2026 학년도 2 학기 평생교육과정 동계방학특강 개설 제안 공모 안내 ] 2026 학년도 2 학기 평생교육과정 동계방학특강 개설 제안 공모를 아래와 같이 실시하오니 많은 신청 바랍니다 . Ⅰ . 강좌개설 신청 - 기간 : 2026.10.26.( 월 ) ~ 11.13.( 금 ) - 방법: e-mail 접수 (gpdls6770@masan.ac.kr) - 제출서류 1. 강의계획서 및 강사추천서 ( 붙임서식 ) 2. 최종학위증명서 , 강의경력증명서 , 관련 자격증 등 증빙서류 (2 학기 개강 강좌는 제외 ) ※ 증빙서류 제출 가능한 경력만 작성 Ⅱ . 강좌운영 계획 - 운영기간 : 2026.12.01.( 화 ) ~ 2027.01.29.( 금 ) ※ 강좌별 운영기간 상이 - 편성기준 1. 주 수 : 8 주 이내 2. 인 원 : 최소 15 명 이상 3. 수강료 : 최소 120,000 원 이상 ( 강좌별 상이 ) 4. 강사료 : 총 수강료 수입의 60% 지급 Ⅲ . 강사 자격조건 1. 평생교육원 운영규정 제 24 조 ( 강사 ) 에 의거하여 학사학위 이상 소지자로 교육 · 연구경력 및 관련분야 근무경력 3 년 이상인 자 - 단 , 강좌의 특성 및 성격에 따라 관련분야 근무경력을 고려하여 운영위원회 심의를 통과한 자 2. 교육공무원법 제 10 조 4 각 호의 결격사유가 없는 자</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -682,11 +682,89 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://cec.ulsan.ac.kr/cec/3978?action=view&amp;no=270342</t>
+          <t>https://lifelong.masan.ac.kr/boardview/000001/295</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026학년도 겨울계절학기 미래시민교육원 강좌 공모 안내</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>부산대학교 미래시민교육원</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2027-02-05</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026 학년도 겨울계절학기 미래시민교육원 강좌 공모 안내 Ⅰ 강좌 공모 가 . 공모개요 ○ 공모 학기 : 2026 학년도 겨울계절학기 ○ 공모 기간 : 2026. 11. 2.( 월 ) ~ 2026. 11. 15.( 일 ) ○ 공모 과정 : 특별과정 * , 일반과정 ** 공모 * 특별과정 : 수강료 , 강사료 배분 비율 , 모집 정원 등이 일반 과정과 다른 강좌 ** 일반과정 : 미래시민교육원에서 공모하여 진행하는 강좌 중 기획과정 특별과정을 제외한 강좌 ※ 이번 겨울계절학기 골프 수업은 골프연습장 (GDR) 환경개선 공사 진행으로 개설이 불가함 ○ 공모자격 및 강좌신청 ( 응모 ) 수 - ( 자격 ) 학사학위 이상의 학위 소지자 ( 단 , 강좌의 특성 및 성격에 따라 관련 분야의 경력 등 고려 가능 ) - ( 응모수 ) 캠퍼스별 강사 1 인당 3 개 이내로 응모 가능 ○ 기존 강좌 , 신규 강좌로 구분하여 공모 - ( 기존강좌 ) 최근 3 년이내 미래시민교육원에서 1 회 이상 개설 이력이 있거나 이와 유사한 강좌 - ( 신규강좌 ) 최근 3 년이내 미래시민교육원에서 개설한 이력이 없는 강좌 ※ 신규강좌 특전 - 1 차 내부 서류 심사 전면 통과 ( 자동 통과 ) 혜택 부여 - 수강생 모집 리플릿 상단에 신규 강좌 전용 섹션 배치하여 집중 홍보 &lt; 공모방법 &gt; - 강좌 공모는 부산대학교 미래시민교육원 홈페이지를 통해 진행 ( 회원가입 필수 ) ▷ [ 로그인 화면 ] → [ 강사 선택 후 로그인 ] → [ 강사진모드 ] → [ 강좌개설신청 ] 메뉴에서 응모 ▷ 강좌명 , 요일 , 시간 등이 포함된 강의계획표와 학력 · 주요경력 · 수상경력 · 자격사항 등을 전산 입력 - 제출서류 ? 책임강사 (1 인강사 ): 학력증명서 , 경력증명서 ( 강의 ? 근무 경력 등 ) 또는 재직증명서 , 주민등록등본 ( 생년월일만 표기 ), 자격증사본 , 개인정보수집 이용 동의서 ( 필수 제출 : 홈페이지 다운로드 후 작성 ) ▷ 보조강사 : 개인정보수집 이용 동의서 ( 필수 제출 : 홈페이지 다운로드 후 작성 ) ▷ 제출 방법 : 관련 서류는 스캔 후 메일 발송 또는 방문 제출 ⇒ 관련 증빙자료는 공모기간 내에 메일 * 또는 방문 ** 하여 제출 * ( 부산캠퍼스 ) zoomboy@pusan.ac.kr , 담당 김대현 051)510-8370 ( 양산캠퍼스 ) zoomboy@pusan.ac.kr , 담당 김대현 051)510-8370 ( 밀양캠퍼스 ) wgson@pusan.ac.kr , 담당 손우기 055)350-5178 ** ( 부산캠퍼스 )NC 백화점 7 층 704 호 행정실 , ( 양산캠퍼스 ) 첨단의생명융합센터 413 호 행정실 , ( 밀양캠퍼스 ) 행정지원본부동 3 층 행정실 &lt; 강의계획표 작성 시 유의사항 &gt; 1. 강좌 개요 : 주요내용 위주 ( 필요성 , 주요 현황 , 발전 가능성 등 ) 로 개조식으로 작성 2. 팀티칭 강좌의 경우는 책임강사 ( 강좌 개설 총괄자 ) 가 입력을 하되 , 강사진 개별 ID 발급 필수 ※ 팀티칭 강좌의 경우 아래 시수</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://sce.pusan.ac.kr/page?menuCD=000000000000561&amp;mode=DETAIL&amp;seq=2598&amp;mainbbsTabIndex=&amp;typeSeqNo=1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>평생교육원 신규 강좌 개설 제안서 안내</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>울산대학교 평생교육원 공지사항</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>울산, 경남</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>울산대학교 평생교육원에서는 참신한 신규 강좌를 모집하오니 관심 있는 강사님들의 많은 신청 바랍니다. 1. 지원 분야 - 평생 교육 관련 전 분야 2. 제출 방법 - 울산대학교 평생교육원 홈페이지 강좌개설제안서 클릭 - 서류 제출 후 전화 확인 - 접수된 개별 신청서는 평생교육원 운영위원회 심의를 통해 최종 개설 확정 후 개별 연락 드립니다. 3. 제출 기한 -2027년 1학기 : 2026.10.01 09:00 ~ 2026.11.20 17:00 -2027년 2학기 : 2027.04.01 09:00 ~ 2027.05.21 17:00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://cec.ulsan.ac.kr/cec/3978?action=view&amp;no=270342</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/gangsaitda/latest.xlsx
+++ b/reports/gangsaitda/latest.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -691,28 +691,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026학년도 겨울계절학기 미래시민교육원 강좌 공모 안내</t>
+          <t>2026학년도 2학기 평생교육과정 동계방학특강 개설 제안 공모 안내</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>부산대학교 미래시민교육원</t>
+          <t>마산대학교 평생교육원 강좌 개설 신청</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026 학년도 겨울계절학기 미래시민교육원 강좌 공모 안내 Ⅰ 강좌 공모 가 . 공모개요 ○ 공모 학기 : 2026 학년도 겨울계절학기 ○ 공모 기간 : 2026. 11. 2.( 월 ) ~ 2026. 11. 15.( 일 ) ○ 공모 과정 : 특별과정 * , 일반과정 ** 공모 * 특별과정 : 수강료 , 강사료 배분 비율 , 모집 정원 등이 일반 과정과 다른 강좌 ** 일반과정 : 미래시민교육원에서 공모하여 진행하는 강좌 중 기획과정 특별과정을 제외한 강좌 ※ 이번 겨울계절학기 골프 수업은 골프연습장 (GDR) 환경개선 공사 진행으로 개설이 불가함 ○ 공모자격 및 강좌신청 ( 응모 ) 수 - ( 자격 ) 학사학위 이상의 학위 소지자 ( 단 , 강좌의 특성 및 성격에 따라 관련 분야의 경력 등 고려 가능 ) - ( 응모수 ) 캠퍼스별 강사 1 인당 3 개 이내로 응모 가능 ○ 기존 강좌 , 신규 강좌로 구분하여 공모 - ( 기존강좌 ) 최근 3 년이내 미래시민교육원에서 1 회 이상 개설 이력이 있거나 이와 유사한 강좌 - ( 신규강좌 ) 최근 3 년이내 미래시민교육원에서 개설한 이력이 없는 강좌 ※ 신규강좌 특전 - 1 차 내부 서류 심사 전면 통과 ( 자동 통과 ) 혜택 부여 - 수강생 모집 리플릿 상단에 신규 강좌 전용 섹션 배치하여 집중 홍보 &lt; 공모방법 &gt; - 강좌 공모는 부산대학교 미래시민교육원 홈페이지를 통해 진행 ( 회원가입 필수 ) ▷ [ 로그인 화면 ] → [ 강사 선택 후 로그인 ] → [ 강사진모드 ] → [ 강좌개설신청 ] 메뉴에서 응모 ▷ 강좌명 , 요일 , 시간 등이 포함된 강의계획표와 학력 · 주요경력 · 수상경력 · 자격사항 등을 전산 입력 - 제출서류 ? 책임강사 (1 인강사 ): 학력증명서 , 경력증명서 ( 강의 ? 근무 경력 등 ) 또는 재직증명서 , 주민등록등본 ( 생년월일만 표기 ), 자격증사본 , 개인정보수집 이용 동의서 ( 필수 제출 : 홈페이지 다운로드 후 작성 ) ▷ 보조강사 : 개인정보수집 이용 동의서 ( 필수 제출 : 홈페이지 다운로드 후 작성 ) ▷ 제출 방법 : 관련 서류는 스캔 후 메일 발송 또는 방문 제출 ⇒ 관련 증빙자료는 공모기간 내에 메일 * 또는 방문 ** 하여 제출 * ( 부산캠퍼스 ) zoomboy@pusan.ac.kr , 담당 김대현 051)510-8370 ( 양산캠퍼스 ) zoomboy@pusan.ac.kr , 담당 김대현 051)510-8370 ( 밀양캠퍼스 ) wgson@pusan.ac.kr , 담당 손우기 055)350-5178 ** ( 부산캠퍼스 )NC 백화점 7 층 704 호 행정실 , ( 양산캠퍼스 ) 첨단의생명융합센터 413 호 행정실 , ( 밀양캠퍼스 ) 행정지원본부동 3 층 행정실 &lt; 강의계획표 작성 시 유의사항 &gt; 1. 강좌 개요 : 주요내용 위주 ( 필요성 , 주요 현황 , 발전 가능성 등 ) 로 개조식으로 작성 2. 팀티칭 강좌의 경우는 책임강사 ( 강좌 개설 총괄자 ) 가 입력을 하되 , 강사진 개별 ID 발급 필수 ※ 팀티칭 강좌의 경우 아래 시수</t>
+          <t>[2026학년도 2학기 평생교육과정 동계방학특강 개설 제안 공모 안내] 2026학년도 2학기 평생교육과정 동계방학특강 개설 제안 공모를 아래와 같이 실시하오니 많은 신청 바랍니다. Ⅰ. 강좌개설 신청 - 기간: 2026.10.26.(월) ~ 11.13.(금) - 방법: e-mail 접수 (gpdls6770@masan.ac.kr) - 제출서류 1. 강의계획서 및 강사추천서 (붙임서식) 2. 최종학위증명서, 강의경력증명서, 관련 자격증 등 증빙서류 (2학기 개강 강좌는 제외) ※ 증빙서류 제출 가능한 경력만 작성 Ⅱ. 강좌운영 계획 - 운영기간: 2026.12.01.(화) ~ 2027.01.29.(금) ※ 강좌별 운영기간 상이 - 편성기준 1. 주 수: 8주 이내 2. 인 원: 최소 15명 이상 3. 수강료: 최소 120,000원 이상 (강좌별 상이) 4. 강사료: 총 수강료 수입의 60% 지급 Ⅲ. 강사 자격조건 1. 평생교육원 운영규정 제24조(강사)에 의거하여 학사학위 이상 소지자로 교육·연구경력 및 관련분야 근무경력 3년 이상인 자 - 단, 강좌의 특성 및 성격에 따라 관련분야 근무경력을 고려하여 운영위원회 심의를 통과한 자 2. 교육공무원법 제10조4 각 호의 결격사유가 없는 자</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -721,7 +721,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://sce.pusan.ac.kr/page?menuCD=000000000000561&amp;mode=DETAIL&amp;seq=2598&amp;mainbbsTabIndex=&amp;typeSeqNo=1</t>
+          <t>https://lifelong.masan.ac.kr/lectopen/view/2026/20/010/999/19</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -730,28 +730,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>평생교육원 신규 강좌 개설 제안서 안내</t>
+          <t>2026학년도 겨울계절학기 미래시민교육원 강좌 공모 안내</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>울산대학교 평생교육원 공지사항</t>
+          <t>부산대학교 미래시민교육원</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>울산, 경남</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>울산대학교 평생교육원에서는 참신한 신규 강좌를 모집하오니 관심 있는 강사님들의 많은 신청 바랍니다. 1. 지원 분야 - 평생 교육 관련 전 분야 2. 제출 방법 - 울산대학교 평생교육원 홈페이지 강좌개설제안서 클릭 - 서류 제출 후 전화 확인 - 접수된 개별 신청서는 평생교육원 운영위원회 심의를 통해 최종 개설 확정 후 개별 연락 드립니다. 3. 제출 기한 -2027년 1학기 : 2026.10.01 09:00 ~ 2026.11.20 17:00 -2027년 2학기 : 2027.04.01 09:00 ~ 2027.05.21 17:00</t>
+          <t>2026 학년도 겨울계절학기 미래시민교육원 강좌 공모 안내 Ⅰ 강좌 공모 가 . 공모개요 ○ 공모 학기 : 2026 학년도 겨울계절학기 ○ 공모 기간 : 2026. 11. 2.( 월 ) ~ 2026. 11. 15.( 일 ) ○ 공모 과정 : 특별과정 * , 일반과정 ** 공모 * 특별과정 : 수강료 , 강사료 배분 비율 , 모집 정원 등이 일반 과정과 다른 강좌 ** 일반과정 : 미래시민교육원에서 공모하여 진행하는 강좌 중 기획과정 특별과정을 제외한 강좌 ※ 이번 겨울계절학기 골프 수업은 골프연습장 (GDR) 환경개선 공사 진행으로 개설이 불가함 ○ 공모자격 및 강좌신청 ( 응모 ) 수 - ( 자격 ) 학사학위 이상의 학위 소지자 ( 단 , 강좌의 특성 및 성격에 따라 관련 분야의 경력 등 고려 가능 ) - ( 응모수 ) 캠퍼스별 강사 1 인당 3 개 이내로 응모 가능 ○ 기존 강좌 , 신규 강좌로 구분하여 공모 - ( 기존강좌 ) 최근 3 년이내 미래시민교육원에서 1 회 이상 개설 이력이 있거나 이와 유사한 강좌 - ( 신규강좌 ) 최근 3 년이내 미래시민교육원에서 개설한 이력이 없는 강좌 ※ 신규강좌 특전 - 1 차 내부 서류 심사 전면 통과 ( 자동 통과 ) 혜택 부여 - 수강생 모집 리플릿 상단에 신규 강좌 전용 섹션 배치하여 집중 홍보 &lt; 공모방법 &gt; - 강좌 공모는 부산대학교 미래시민교육원 홈페이지를 통해 진행 ( 회원가입 필수 ) ▷ [ 로그인 화면 ] → [ 강사 선택 후 로그인 ] → [ 강사진모드 ] → [ 강좌개설신청 ] 메뉴에서 응모 ▷ 강좌명 , 요일 , 시간 등이 포함된 강의계획표와 학력 · 주요경력 · 수상경력 · 자격사항 등을 전산 입력 - 제출서류 ? 책임강사 (1 인강사 ): 학력증명서 , 경력증명서 ( 강의 ? 근무 경력 등 ) 또는 재직증명서 , 주민등록등본 ( 생년월일만 표기 ), 자격증사본 , 개인정보수집 이용 동의서 ( 필수 제출 : 홈페이지 다운로드 후 작성 ) ▷ 보조강사 : 개인정보수집 이용 동의서 ( 필수 제출 : 홈페이지 다운로드 후 작성 ) ▷ 제출 방법 : 관련 서류는 스캔 후 메일 발송 또는 방문 제출 ⇒ 관련 증빙자료는 공모기간 내에 메일 * 또는 방문 ** 하여 제출 * ( 부산캠퍼스 ) zoomboy@pusan.ac.kr , 담당 김대현 051)510-8370 ( 양산캠퍼스 ) zoomboy@pusan.ac.kr , 담당 김대현 051)510-8370 ( 밀양캠퍼스 ) wgson@pusan.ac.kr , 담당 손우기 055)350-5178 ** ( 부산캠퍼스 )NC 백화점 7 층 704 호 행정실 , ( 양산캠퍼스 ) 첨단의생명융합센터 413 호 행정실 , ( 밀양캠퍼스 ) 행정지원본부동 3 층 행정실 &lt; 강의계획표 작성 시 유의사항 &gt; 1. 강좌 개요 : 주요내용 위주 ( 필요성 , 주요 현황 , 발전 가능성 등 ) 로 개조식으로 작성 2. 팀티칭 강좌의 경우는 책임강사 ( 강좌 개설 총괄자 ) 가 입력을 하되 , 강사진 개별 ID 발급 필수 ※ 팀티칭 강좌의 경우 아래 시수</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -760,11 +760,50 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://cec.ulsan.ac.kr/cec/3978?action=view&amp;no=270342</t>
+          <t>https://sce.pusan.ac.kr/page?menuCD=000000000000561&amp;mode=DETAIL&amp;seq=2598&amp;mainbbsTabIndex=&amp;typeSeqNo=1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>평생교육원 신규 강좌 개설 제안서 안내</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>울산대학교 평생교육원 공지사항</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>울산, 경남</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2027-05-21</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>울산대학교 평생교육원에서는 참신한 신규 강좌를 모집하오니 관심 있는 강사님들의 많은 신청 바랍니다. 1. 지원 분야 - 평생 교육 관련 전 분야 2. 제출 방법 - 울산대학교 평생교육원 홈페이지 강좌개설제안서 클릭 - 서류 제출 후 전화 확인 - 접수된 개별 신청서는 평생교육원 운영위원회 심의를 통해 최종 개설 확정 후 개별 연락 드립니다. 3. 제출 기한 -2027년 1학기 : 2026.10.01 09:00 ~ 2026.11.20 17:00 -2027년 2학기 : 2027.04.01 09:00 ~ 2027.05.21 17:00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://cec.ulsan.ac.kr/cec/3978?action=view&amp;no=270342</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
